--- a/lab4/soc.xlsx
+++ b/lab4/soc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tjape/Documents/labs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\agile-hw\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63539A3-7976-0F4B-86E7-813452FEBB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CB0FE6-5555-4BA1-B60F-3A96D61D47F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5440" yWindow="4240" windowWidth="26180" windowHeight="16440" activeTab="1" xr2:uid="{3275062E-E941-4C44-B786-B260B7FE7C7F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{3275062E-E941-4C44-B786-B260B7FE7C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Map" sheetId="1" r:id="rId1"/>
@@ -617,14 +617,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F4C322E-31B3-4946-83B0-6D906636E698}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="12.1640625" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="23.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.19921875" customWidth="1"/>
+    <col min="5" max="5" width="11.69921875" customWidth="1"/>
+    <col min="8" max="8" width="23.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -650,7 +650,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -676,7 +676,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -702,7 +702,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -728,7 +728,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -762,9 +762,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8554253-EFF4-DF4A-9A3D-E0A146250D2C}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -784,7 +784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -844,7 +844,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -864,7 +864,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -884,7 +884,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -912,9 +912,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC93B92-A4C4-CC41-BDFB-9BB866D116F4}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -934,7 +934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>56</v>
       </c>
@@ -951,19 +951,19 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E7" s="2"/>
     </row>
   </sheetData>
@@ -974,9 +974,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B4F0480-79EE-0544-BD4A-D1E1D23B917D}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -996,7 +996,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>45</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E6" s="2"/>
     </row>
   </sheetData>
